--- a/LISTAS/mi/DRYWALL NAC..xlsx
+++ b/LISTAS/mi/DRYWALL NAC..xlsx
@@ -625,7 +625,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45163.60863905559</v>
+        <v>45253</v>
       </c>
       <c r="F1" s="6" t="n"/>
       <c r="G1" s="6" t="n"/>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3804.775</v>
+        <v>4375.491</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="1">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4239.113</v>
+        <v>4874.98</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="1">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>5288.486</v>
+        <v>6081.759</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="1">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>6428.162</v>
+        <v>7392.386</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="1">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>7392.373</v>
+        <v>8501.228999999999</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="1">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>7826.709</v>
+        <v>9000.715</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="1">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>11302.385</v>
+        <v>12997.743</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="1">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>9729.106</v>
+        <v>11188.472</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="1">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>11414.333</v>
+        <v>13126.483</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="1">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>12314.254</v>
+        <v>14161.392</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="1">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>9097.525</v>
+        <v>10462.154</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="1">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>8469.553</v>
+        <v>9739.986000000001</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="1">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>9937.569</v>
+        <v>11428.204</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="1">
@@ -1024,7 +1024,9 @@
           <t>4 x 41</t>
         </is>
       </c>
-      <c r="D27" s="16" t="n"/>
+      <c r="D27" s="16" t="n">
+        <v>14585.142</v>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="1">
       <c r="A28" s="17" t="inlineStr">
@@ -1043,7 +1045,7 @@
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>10163.444</v>
+        <v>11687.961</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="1">
@@ -1063,7 +1065,7 @@
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>12265.639</v>
+        <v>14105.485</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="1">
@@ -1083,7 +1085,7 @@
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>15219.094</v>
+        <v>17501.958</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="1">
@@ -1103,7 +1105,7 @@
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>17755.637</v>
+        <v>20418.983</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="1">
@@ -1132,15 +1134,6 @@
       </c>
       <c r="C35" s="6" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>

--- a/LISTAS/mi/DRYWALL NAC..xlsx
+++ b/LISTAS/mi/DRYWALL NAC..xlsx
@@ -625,7 +625,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="F1" s="6" t="n"/>
       <c r="G1" s="6" t="n"/>

--- a/LISTAS/mi/DRYWALL NAC..xlsx
+++ b/LISTAS/mi/DRYWALL NAC..xlsx
@@ -625,7 +625,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="F1" s="6" t="n"/>
       <c r="G1" s="6" t="n"/>

--- a/LISTAS/mi/DRYWALL NAC..xlsx
+++ b/LISTAS/mi/DRYWALL NAC..xlsx
@@ -625,7 +625,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="F1" s="6" t="n"/>
       <c r="G1" s="6" t="n"/>

--- a/LISTAS/mi/DRYWALL NAC..xlsx
+++ b/LISTAS/mi/DRYWALL NAC..xlsx
@@ -625,7 +625,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="F1" s="6" t="n"/>
       <c r="G1" s="6" t="n"/>

--- a/LISTAS/mi/DRYWALL NAC..xlsx
+++ b/LISTAS/mi/DRYWALL NAC..xlsx
@@ -11,14 +11,14 @@
     <sheet name="Hoja3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -27,11 +27,6 @@
       <name val="Arial Black"/>
       <family val="2"/>
       <i val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial Black"/>
-      <family val="2"/>
       <sz val="14"/>
     </font>
     <font>
@@ -56,11 +51,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color indexed="14"/>
       <sz val="12"/>
     </font>
     <font>
@@ -146,58 +136,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,523 +606,531 @@
   <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
-    <col width="14.28515625" customWidth="1" style="1" min="1" max="1"/>
-    <col width="14.140625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="17.7109375" customWidth="1" style="1" min="3" max="3"/>
-    <col width="22.7109375" customWidth="1" style="1" min="4" max="4"/>
+    <col width="14.28515625" customWidth="1" style="20" min="1" max="1"/>
+    <col width="14.140625" customWidth="1" style="20" min="2" max="2"/>
+    <col width="17.7109375" customWidth="1" style="20" min="3" max="3"/>
+    <col width="22.7109375" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="n">
-        <v>45266</v>
-      </c>
-      <c r="F1" s="6" t="n"/>
-      <c r="G1" s="6" t="n"/>
+      <c r="A1" s="19" t="n">
+        <v>45261.57771502566</v>
+      </c>
+      <c r="F1" s="5" t="n"/>
+      <c r="G1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="22.5" customHeight="1" s="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="22.5" customHeight="1" s="20">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>LA PAZ 28  -  HAEDO                           4460-2005</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="22.5" customHeight="1" s="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1" s="20">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>BUENOS AIRES                   luquearti@gmail.com</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="19" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>____________________________________________________________________________________</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="20">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TORNILLOS DRYWALL NAC.</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">PUNTA AGUJA , Fosfatizados NEGRO ,Ranura Philips , </t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      Rosca paso gureso</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="20">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>COD.</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>MEDIDA</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Equivalencia</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>PRECIO por MILLAR</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="1">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="14" ht="15.75" customHeight="1" s="20">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>DRYN-099</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>6 x 5/8</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>3,5 x 15,9</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
-        <v>4375.491</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="D14" s="15" t="n">
+        <v>6088.49</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="20">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>DRYN-100</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>6 x 3/4</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>3,5 x 19</t>
         </is>
       </c>
-      <c r="D15" s="16" t="n">
-        <v>4874.98</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="D15" s="15" t="n">
+        <v>6783.53</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="20">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>DRYN-101</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>6 x 1</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>3,5 x 25</t>
         </is>
       </c>
-      <c r="D16" s="16" t="n">
-        <v>6081.759</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" s="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="D16" s="15" t="n">
+        <v>8462.76</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="20">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>DRYN-102</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>6 x 1 1/4</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>3,5 x 32</t>
         </is>
       </c>
-      <c r="D17" s="16" t="n">
-        <v>7392.386</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="D17" s="15" t="n">
+        <v>10286.5</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="20">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>DRYN-103</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>6 x 1 1/2</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>3,5 x 38</t>
         </is>
       </c>
-      <c r="D18" s="16" t="n">
-        <v>8501.228999999999</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="D18" s="15" t="n">
+        <v>11829.46</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="20">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>DRYN-104</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>6 x 1 5/8</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>3,5 x 41</t>
         </is>
       </c>
-      <c r="D19" s="16" t="n">
-        <v>9000.715</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="D19" s="15" t="n">
+        <v>12524.49</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>DRYN-105</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>6 x 1 3/4</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>3,5 x 44</t>
         </is>
       </c>
-      <c r="D20" s="16" t="n">
-        <v>12997.743</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="D20" s="15" t="n">
+        <v>18086.35</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="20">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>DRYN-106</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>6 x 2</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>3,5 x 51</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n">
-        <v>11188.472</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="D21" s="15" t="n">
+        <v>15568.75</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="20">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>DRYN-107</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>6 x 2 1/4</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>3,5 x 56</t>
         </is>
       </c>
-      <c r="D22" s="16" t="n">
-        <v>13126.483</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="D22" s="15" t="n">
+        <v>18265.5</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="20">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>DRYN-107A</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>6 x 2 1/2</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>3,5 x 63</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
-        <v>14161.392</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="D23" s="15" t="n">
+        <v>19705.57</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="20">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>DRYN-108Z</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>8 x 1</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>4 x 25</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>10462.154</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="D24" s="15" t="n">
+        <v>14558.08</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="20">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>DRYN-109</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>8 x 1 1/4</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>4 x 31,7</t>
         </is>
       </c>
-      <c r="D25" s="16" t="n">
-        <v>9739.986000000001</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" s="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="D25" s="15" t="n">
+        <v>13553.19</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="20">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>DRYN-110</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>8 x 1 1/2</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>4 x 38</t>
         </is>
       </c>
-      <c r="D26" s="16" t="n">
-        <v>11428.204</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="D26" s="15" t="n">
+        <v>15902.34</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="20">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>DRYN-110/0</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>8 x 1 5/8</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>4 x 41</t>
         </is>
       </c>
-      <c r="D27" s="16" t="n">
-        <v>14585.142</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="D27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="20">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>DRYN-110/1</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>8 x 1 3/4</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>4 x 44</t>
         </is>
       </c>
-      <c r="D28" s="16" t="n">
-        <v>11687.961</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="1">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="D28" s="15" t="n">
+        <v>16263.79</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="20">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>DRYN-111</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>8 x 2</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>4 x 51</t>
         </is>
       </c>
-      <c r="D29" s="16" t="n">
-        <v>14105.485</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="D29" s="15" t="n">
+        <v>19627.78</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="20">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>DRYN-112</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>8 x 2 1/2</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>4 x 63</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
-        <v>17501.958</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" s="1">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="D30" s="15" t="n">
+        <v>24353.97</v>
+      </c>
+      <c r="F30" s="21" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="20">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>DRYN-113</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>8 x 3</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>4 x 76</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n">
-        <v>20418.983</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" s="1">
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
+      <c r="D31" s="15" t="n">
+        <v>28413.01</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="20">
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="1">
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="20">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>PRECIO POR MIL UNIDADES</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="1">
-      <c r="B35" s="15" t="inlineStr">
+      <c r="C34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="20">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>ENVASE POR 500 UNIDADES</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n"/>
-    </row>
+      <c r="C35" s="5" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
